--- a/ksoft/docs/stock/Bestand_Finish Folie_Set up_details.XLSX
+++ b/ksoft/docs/stock/Bestand_Finish Folie_Set up_details.XLSX
@@ -12480,13 +12480,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C856CF7-3364-4E9B-B869-49C14357C7FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBE9B163-9B47-43CC-A6A1-C079EED59946}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{462A2DA9-ED21-4410-8302-A5D5AE74FEE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B198D39-55DA-4813-A3D5-D3AD19381537}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6319944-2D41-41C7-BB7C-7B331D438A4D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCFF21F1-117E-4447-BAA5-E08F35B08061}"/>
 </file>
--- a/ksoft/docs/stock/Bestand_Finish Folie_Set up_details.XLSX
+++ b/ksoft/docs/stock/Bestand_Finish Folie_Set up_details.XLSX
@@ -12480,13 +12480,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBE9B163-9B47-43CC-A6A1-C079EED59946}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C856CF7-3364-4E9B-B869-49C14357C7FA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B198D39-55DA-4813-A3D5-D3AD19381537}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{462A2DA9-ED21-4410-8302-A5D5AE74FEE4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCFF21F1-117E-4447-BAA5-E08F35B08061}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6319944-2D41-41C7-BB7C-7B331D438A4D}"/>
 </file>